--- a/office/data/教师资料.xlsx
+++ b/office/data/教师资料.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cnplaman\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBF16D1-5D67-45D9-89A7-86C3B133EDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94236B98-8638-47AA-BDB6-CE0F76AEE83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{08D40B36-C0BC-4269-A5D4-A5AA6F531EAB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{08D40B36-C0BC-4269-A5D4-A5AA6F531EAB}"/>
   </bookViews>
   <sheets>
     <sheet name="教师资料" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,20 +173,6 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -211,14 +197,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -534,341 +516,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4227E4-E788-45AB-BD5A-3F8C562F493B}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8.88671875" style="1"/>
-    <col min="12" max="13" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2">
         <v>21925</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2">
         <v>8300</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3">
         <v>25122</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3">
         <v>7300</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4">
         <v>20950</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4">
         <v>7300</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5">
         <v>22132</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5">
         <v>9000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6">
         <v>21220</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6">
         <v>8600</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7">
         <v>21248</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7">
         <v>7800</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8">
         <v>22951</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8">
         <v>8300</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9">
         <v>20616</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9">
         <v>8600</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10">
         <v>21956</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10">
         <v>9500</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11">
         <v>25851</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11">
         <v>7800</v>
       </c>
     </row>
@@ -884,7 +864,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938BD8C2-0C06-47F6-B1D2-BAE8CE47E925}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/office/data/教师资料.xlsx
+++ b/office/data/教师资料.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94236B98-8638-47AA-BDB6-CE0F76AEE83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8151BE8C-13D5-414D-8794-9C115E934E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{08D40B36-C0BC-4269-A5D4-A5AA6F531EAB}"/>
   </bookViews>
@@ -26,132 +26,133 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
   <si>
     <t>职工编号</t>
   </si>
   <si>
+    <t>张京平</t>
+  </si>
+  <si>
+    <t>甘小间</t>
+  </si>
+  <si>
+    <t>何立立</t>
+  </si>
+  <si>
+    <t>教授</t>
+  </si>
+  <si>
+    <t>戴江宁</t>
+  </si>
+  <si>
+    <t>方洪海</t>
+  </si>
+  <si>
+    <t>徐万万</t>
+  </si>
+  <si>
+    <t>李宇红</t>
+  </si>
+  <si>
+    <t>田皎皎</t>
+  </si>
+  <si>
+    <t>田立萍</t>
+  </si>
+  <si>
+    <t>职工姓名</t>
+  </si>
+  <si>
+    <t>性别</t>
+  </si>
+  <si>
+    <t>学历</t>
+  </si>
+  <si>
+    <t>职称编码</t>
+  </si>
+  <si>
+    <t>职称</t>
+  </si>
+  <si>
+    <t>出生日期</t>
+  </si>
+  <si>
+    <t>部门</t>
+  </si>
+  <si>
+    <t>工资</t>
+  </si>
+  <si>
+    <t>男</t>
+  </si>
+  <si>
+    <t>博士</t>
+  </si>
+  <si>
+    <t>副教授</t>
+  </si>
+  <si>
+    <t>计算机科学系</t>
+  </si>
+  <si>
+    <t>女</t>
+  </si>
+  <si>
+    <t>电子系</t>
+  </si>
+  <si>
+    <t>讲师</t>
+  </si>
+  <si>
+    <t>李洪文</t>
+  </si>
+  <si>
+    <t>硕士</t>
+  </si>
+  <si>
+    <t>学士</t>
+  </si>
+  <si>
     <t>001</t>
-  </si>
-  <si>
-    <t>张京平</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>007</t>
-  </si>
-  <si>
-    <t>甘小间</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>何立立</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>009</t>
-  </si>
-  <si>
-    <t>教授</t>
-  </si>
-  <si>
-    <t>008</t>
-  </si>
-  <si>
-    <t>戴江宁</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>方洪海</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>010</t>
-  </si>
-  <si>
-    <t>徐万万</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>李宇红</t>
-  </si>
-  <si>
-    <t>005</t>
-  </si>
-  <si>
-    <t>田皎皎</t>
-  </si>
-  <si>
-    <t>006</t>
-  </si>
-  <si>
-    <t>田立萍</t>
-  </si>
-  <si>
-    <t>职工姓名</t>
-  </si>
-  <si>
-    <t>性别</t>
-  </si>
-  <si>
-    <t>学历</t>
-  </si>
-  <si>
-    <t>职称编码</t>
-  </si>
-  <si>
-    <t>职称</t>
-  </si>
-  <si>
-    <t>出生日期</t>
-  </si>
-  <si>
-    <t>部门</t>
-  </si>
-  <si>
-    <t>工资</t>
-  </si>
-  <si>
-    <t>男</t>
-  </si>
-  <si>
-    <t>博士</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>副教授</t>
-  </si>
-  <si>
-    <t>计算机科学系</t>
-  </si>
-  <si>
-    <t>女</t>
-  </si>
-  <si>
-    <t>电子系</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>讲师</t>
-  </si>
-  <si>
-    <t>李洪文</t>
-  </si>
-  <si>
-    <t>硕士</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>学士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -197,8 +198,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -525,7 +532,8 @@
     <col min="7" max="7" width="15.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.75" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="3.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.75" bestFit="1" customWidth="1"/>
@@ -538,315 +546,315 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G2" s="1">
+        <v>21925</v>
+      </c>
+      <c r="H2" t="s">
         <v>22</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2">
-        <v>21925</v>
-      </c>
-      <c r="H2" t="s">
-        <v>33</v>
       </c>
       <c r="I2">
         <v>8300</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
+      <c r="A3" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3">
+        <v>25</v>
+      </c>
+      <c r="G3" s="1">
         <v>25122</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I3">
         <v>7300</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>11</v>
+      <c r="A4" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1">
         <v>20950</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I4">
         <v>7300</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>15</v>
+      <c r="A5" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" t="s">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1">
         <v>22132</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I5">
         <v>9000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
+      <c r="A6" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1">
         <v>21220</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I6">
         <v>8600</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>19</v>
+      <c r="A7" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="G7" s="1">
         <v>21248</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I7">
         <v>7800</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>3</v>
+      <c r="A8" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1">
         <v>22951</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I8">
         <v>8300</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>9</v>
+      <c r="A9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1">
         <v>20616</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I9">
         <v>8600</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>7</v>
+      <c r="A10" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
+        <v>27</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
         <v>21956</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I10">
         <v>9500</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>13</v>
+      <c r="A11" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11">
+        <v>25</v>
+      </c>
+      <c r="G11" s="1">
         <v>25851</v>
       </c>
       <c r="H11" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I11">
         <v>7800</v>
